--- a/data/imports/templates/influencers_template.xlsx
+++ b/data/imports/templates/influencers_template.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -460,9 +460,17 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="19.8" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,30 +505,70 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>팔로워수</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>상황</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>첫회신일</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>회신계정</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>전화번호</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>카카오톡ID</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>발송차수</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>최종발송일</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>마지막사용계정ID</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>히스토리</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -544,30 +592,70 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>미발송/발송중/답장받음/컨펌/거절/비공개</t>
+          <t>예: 15.1만 / 1.2M</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>패션/뷰티/푸드 등</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>내부 담당자명</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>미발송/dm 소통중/회신중/미팅 fix/카톡 소통중/이탈/컨펌</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>우리 계정 인스타ID (회신 받은 계정)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>셀러 이메일</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>셀러 연락처</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>카톡 ID</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>숫자</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>우리 계정의 인스타ID</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -591,21 +679,41 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>15.1만</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>패션</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>김동완</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>미발송</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
